--- a/rag_logs.xlsx
+++ b/rag_logs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,164 +458,82 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>what is his name?</t>
+          <t>work experince realted ot LLm's</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
-        <is>
-          <t>Chaitanya Reddy
-Binghamton, NY | (607) 595-8133 | chaitanya3168@gmail.com | https://www.linkedin.com/in/chaitanya-reddy-genai/</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>PROFESSIONAL SUMMARY</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>EDUCATION
-Binghamton University, State University of New York, Thomas J. Watson College of Engineering and Applied Science
-Masters in Computer Science
-VIT-AP University, India                  
-Bachelor of Science in Computer Science</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Chaitanya Reddy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>what are the top achievements</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>EDUCATION
-Binghamton University, State University of New York, Thomas J. Watson College of Engineering and Applied Science
-Masters in Computer Science
-VIT-AP University, India                  
-Bachelor of Science in Computer Science</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Redefined the core “active member” metric by redesigning ETL filtering logic using pyspark and SQL, correcting inflated counts from 10M to 5.6M users (44% reduction) and improving reliability of downstream dashboards and product KPIs.
-Improved ranking precision, increasing the share of recently active members in the top 700 distress scores from 65% to 90%, and in the top 2000 from 50% to 85%</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
         <is>
           <t>TECHNICAL SKILLS
 Big Data Technologies: Databricks, PySpark, Apache Spark
 Programming Languages: Python, SQL, PySpark, Excel VBA
 Databases: Snowflake, BigQuery, UnityCatalog, Azure SQL
-Machine Learning &amp; NLP: GPT-4o, prompt engineering, few-shot learning, sentiment analysis, RFM modeling, predictive modeling, anomaly detection, tokenization, lemmatization, text preprocessing</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Redefined the core “active member” metric by redesigning ETL filtering logic, correcting inflated counts from 10M to 5.6M users (44% reduction), and improving reliability of downstream dashboards and product KPIs.
-Improved ranking precision in recently active members for top 700 distress scores (increased share from 65% to 90%) and top 2000 (increased share from 50% to 85%).</t>
+Machine Learning &amp; NLP: GPT-4o, prompt engineering, few-shot learning, sentiment analysis, RFM modeling, predictive modeling, anomaly detection, tokenization, lemmatization, text preprocessing
+Data Engineering &amp; Workflow Automation: ETL/ELT pipeline development, Databricks Jobs, MLflow, automated scoring pipelines
+Data Visualization: Tableau, Excel
+PROFESSIONAL EXPERIENCE
+BCBSND,  Data Scientist  | Remote			           	  	                         	  		                    Feb 2026 – present</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PROFESSIONAL SUMMARY
+Innovative data scientist with over 2 years of experience applying SQL, Python, and statistical analysis to drive data-informed product and operational decisions. Skilled in designing and analyzing experiments (including A/B testing), defining and monitoring core product metrics, and transforming ambiguous business questions into structured analytical insights. Proven experience building scalable data pipelines, behavioral models, and dashboards to analyze user engagement and customer experience across large datasets. Adept at collaborating with product managers, engineers, and cross-functional stakeholders to evaluate product changes, measure impact, and deliver actionable recommendations that improve user experience and operational efficiency.
+TECHNICAL SKILLS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Accenture , Data Scientist | India  				   		        			             June 2021 – June 2022
+Defined and maintained core business and product metrics using SQL and Tableau dashboards, enabling stakeholders to monitor system performance, user engagement trends, and operational KPIs.
+Conducted deep-dive analyses using SQL and Python to investigate performance issues and uncover behavioral patterns in large datasets, translating ambiguous business questions into structured analytical problems.
+Built scalable data pipelines using Google BigQuery, Dataflow, and GCS to process 1M+ records daily, ensuring reliable datasets for reporting, experimentation, and analytics workflows.
+EDUCATION</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Not mentioned in the resume.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>what is the experience ralted to azure?</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Built a Compliance 360 Q&amp;A solution using Microsoft Copilot Studio integrated with a knowledge base of 400+ regulatory and internal policy documents, enabling efficient, real-time retrieval of compliance information.
-Developed an EDI 834 data transformation pipeline leveraging Microsoft Power Automate and Azure Functions(Python) to process enrollment data and convert it into structured Excel reports, improving data accessibility and reducing manual processing time.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Implemented data validation, transformation, and error-handling logic using Python and Power Platform workflows, ensuring accuracy, consistency, and reliability of healthcare data pipelines.
-United Health Group,  Data Scientist  | Remote			           	  	                         	  		  Jan 2025 – Feb 2026
-Built product analytics pipelines in Azure Databricks using PySpark, SQL, and Python to monitor member engagement metrics across claims, calls, portal usage, and financial interactions.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>work experince related to LLM;s</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>TECHNICAL SKILLS
 Big Data Technologies: Databricks, PySpark, Apache Spark
 Programming Languages: Python, SQL, PySpark, Excel VBA
 Databases: Snowflake, BigQuery, UnityCatalog, Azure SQL
-Machine Learning &amp; NLP: GPT-4o, prompt engineering, few-shot learning, sentiment analysis, RFM modeling, predictive modeling, anomaly detection, tokenization, lemmatization, text preprocessing</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Azure Functions (Python) was used to process enrollment data and convert it into structured Excel reports, improving data accessibility and reducing manual processing time.
-Also, Azure Databricks was used to build product analytics pipelines in PySpark, SQL, and Python to monitor member engagement metrics across claims, calls, portal usage, and financial interactions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>what ishis NLP expereince?</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>PROFESSIONAL SUMMARY</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Leveraged LLM-based sentiment analysis and topic modeling on member call transcripts to surface trending distress patterns and behavioral signals, enabling proactive intervention strategies across large member populations.
-Designed and implemented AI-powered Reason for Distress (RFD) pipelines by integrating OpenAI GPT-4.0 with zero shot and few-shot learning prompt templates to extract insights from member call transcripts.on outcomes for cross-functional stakeholder</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Conducted sentiment analysis and deployed topic modeling (LDA, SVD) to identify root causes of customer dissatisfaction and cluster feedback thematically
-Generated actionable insights that contributed to a 12% reduction in repeat call volume, improving customer service effectiveness
-Delivered interactive dashboards and detailed analytical reports to business stakeholders, supporting demand planning and CX strategy alignment</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Designed and implemented AI-powered Reason for Distress (RFD) pipelines by integrating OpenAI GPT-4.0 with zero-shot and few-shot learning prompt templates to extract insights from member call transcripts.
-Also, Leveraged LLM-based sentiment analysis and topic modeling on member call transcripts to surface trending distress patterns and behavioral signals, enabling proactive intervention strategies across large member populations.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>any experince related to copilot or. miscrosft?</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Designed and deployed automated contract review workflows using Microsoft Copilot Studio, Microsoft Power Automate, and Azure Functions (Python) to analyze healthcare agreements and generate structured, standardized output documents, improving consistency and reducing manual review effort.</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Built a Compliance 360 Q&amp;A solution using Microsoft Copilot Studio integrated with a knowledge base of 400+ regulatory and internal policy documents, enabling efficient, real-time retrieval of compliance information.
-Developed an EDI 834 data transformation pipeline leveraging Microsoft Power Automate and Azure Functions(Python) to process enrollment data and convert it into structured Excel reports, improving data accessibility and reducing manual processing time.</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>PROFESSIONAL SUMMARY</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Designed and deployed automated contract review workflows using Microsoft Copilot Studio.
-Built a Compliance 360 Q&amp;A solution using Microsoft Copilot Studio integrated with a knowledge base of 400+ regulatory and internal policy documents, enabling efficient, real-time retrieval of compliance information.</t>
+Machine Learning &amp; NLP: GPT-4o, prompt engineering, few-shot learning, sentiment analysis, RFM modeling, predictive modeling, anomaly detection, tokenization, lemmatization, text preprocessing
+Data Engineering &amp; Workflow Automation: ETL/ELT pipeline development, Databricks Jobs, MLflow, automated scoring pipelines
+Data Visualization: Tableau, Excel
+PROFESSIONAL EXPERIENCE
+BCBSND,  Data Scientist  | Remote			           	  	                         	  		                    Feb 2026 – present</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PROFESSIONAL SUMMARY
+Innovative data scientist with over 2 years of experience applying SQL, Python, and statistical analysis to drive data-informed product and operational decisions. Skilled in designing and analyzing experiments (including A/B testing), defining and monitoring core product metrics, and transforming ambiguous business questions into structured analytical insights. Proven experience building scalable data pipelines, behavioral models, and dashboards to analyze user engagement and customer experience across large datasets. Adept at collaborating with product managers, engineers, and cross-functional stakeholders to evaluate product changes, measure impact, and deliver actionable recommendations that improve user experience and operational efficiency.
+TECHNICAL SKILLS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Accenture , Data Scientist | India  				   		        			             June 2021 – June 2022
+Defined and maintained core business and product metrics using SQL and Tableau dashboards, enabling stakeholders to monitor system performance, user engagement trends, and operational KPIs.
+Conducted deep-dive analyses using SQL and Python to investigate performance issues and uncover behavioral patterns in large datasets, translating ambiguous business questions into structured analytical problems.
+Built scalable data pipelines using Google BigQuery, Dataflow, and GCS to process 1M+ records daily, ensuring reliable datasets for reporting, experimentation, and analytics workflows.
+EDUCATION</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>It is mentioned that he worked with GPT-4o, which implies a relationship with Large Language Models (LLMs).</t>
         </is>
       </c>
     </row>

--- a/rag_logs.xlsx
+++ b/rag_logs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,6 +537,612 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>what are all thge tools and technologies used.</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TECHNICAL SKILLS
+Big Data Technologies: Databricks, PySpark, Apache Spark
+Programming Languages: Python, SQL, PySpark, Excel VBA
+Databases: Snowflake, BigQuery, UnityCatalog, Azure SQL
+Machine Learning &amp; NLP: GPT-4o, prompt engineering, few-shot learning, sentiment analysis, RFM modeling, predictive modeling, anomaly detection, tokenization, lemmatization, text preprocessing
+Data Engineering &amp; Workflow Automation: ETL/ELT pipeline development, Databricks Jobs, MLflow, automated scoring pipelines
+Data Visualization: Tableau, Excel
+PROFESSIONAL EXPERIENCE
+BCBSND,  Data Scientist  | Remote			           	  	                         	  		                    Feb 2026 – present</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PROFESSIONAL SUMMARY
+Innovative data scientist with over 2 years of experience applying SQL, Python, and statistical analysis to drive data-informed product and operational decisions. Skilled in designing and analyzing experiments (including A/B testing), defining and monitoring core product metrics, and transforming ambiguous business questions into structured analytical insights. Proven experience building scalable data pipelines, behavioral models, and dashboards to analyze user engagement and customer experience across large datasets. Adept at collaborating with product managers, engineers, and cross-functional stakeholders to evaluate product changes, measure impact, and deliver actionable recommendations that improve user experience and operational efficiency.
+TECHNICAL SKILLS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PROFESSIONAL EXPERIENCE
+BCBSND,  Data Scientist  | Remote			           	  	                         	  		                    Feb 2026 – present
+Designed and deployed automated contract review workflows using Microsoft Copilot Studio, Microsoft Power Automate, and Azure Functions (Python) to analyze healthcare agreements and generate structured, standardized output documents, improving consistency and reducing manual review effort.
+Built a Compliance 360 Q&amp;A solution using Microsoft Copilot Studio integrated with a knowledge base of 400+ regulatory and internal policy documents, enabling efficient, real-time retrieval of compliance information.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Microsoft Copilot Studio, Microsoft Power Automate, Azure Functions (Python), Google BigQuery, Dataflow, GCS, Tableau, Excel, VBA, UnityCatalog, Azure SQL, Databricks, PySpark, Snowflake, BigQuery, UnityCatalog, Python, SQL, Excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CLoud techinologies</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TECHNICAL SKILLS
+Big Data Technologies: Databricks, PySpark, Apache Spark
+Programming Languages: Python, SQL, PySpark, Excel VBA
+Databases: Snowflake, BigQuery, UnityCatalog, Azure SQL
+Machine Learning &amp; NLP: GPT-4o, prompt engineering, few-shot learning, sentiment analysis, RFM modeling, predictive modeling, anomaly detection, tokenization, lemmatization, text preprocessing
+Data Engineering &amp; Workflow Automation: ETL/ELT pipeline development, Databricks Jobs, MLflow, automated scoring pipelines
+Data Visualization: Tableau, Excel
+PROFESSIONAL EXPERIENCE
+BCBSND,  Data Scientist  | Remote			           	  	                         	  		                    Feb 2026 – present</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Developed an EDI 834 data transformation pipeline leveraging Microsoft Power Automate and Azure Functions(Python) to process enrollment data and convert it into structured Excel reports, improving data accessibility and reducing manual processing time.
+Implemented data validation, transformation, and error-handling logic using Python and Power Platform workflows, ensuring accuracy, consistency, and reliability of healthcare data pipelines.
+United Health Group,  Data Scientist  | Remote			           	  	                         	  		  Jan 2025 – Feb 2026
+Built product analytics pipelines in Azure Databricks using PySpark, SQL, and Python to monitor member engagement metrics across claims, calls, portal usage, and financial interactions.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Accenture , Data Scientist | India  				   		        			             June 2021 – June 2022
+Defined and maintained core business and product metrics using SQL and Tableau dashboards, enabling stakeholders to monitor system performance, user engagement trends, and operational KPIs.
+Conducted deep-dive analyses using SQL and Python to investigate performance issues and uncover behavioral patterns in large datasets, translating ambiguous business questions into structured analytical problems.
+Built scalable data pipelines using Google BigQuery, Dataflow, and GCS to process 1M+ records daily, ensuring reliable datasets for reporting, experimentation, and analytics workflows.
+EDUCATION</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Azure Functions, Azure SQL, Google Cloud (BigQuery, Dataflow), Microsoft Power Automate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>number of years experince in pthon</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TECHNICAL SKILLS
+Big Data Technologies: Databricks, PySpark, Apache Spark
+Programming Languages: Python, SQL, PySpark, Excel VBA
+Databases: Snowflake, BigQuery, UnityCatalog, Azure SQL
+Machine Learning &amp; NLP: GPT-4o, prompt engineering, few-shot learning, sentiment analysis, RFM modeling, predictive modeling, anomaly detection, tokenization, lemmatization, text preprocessing
+Data Engineering &amp; Workflow Automation: ETL/ELT pipeline development, Databricks Jobs, MLflow, automated scoring pipelines
+Data Visualization: Tableau, Excel
+PROFESSIONAL EXPERIENCE
+BCBSND,  Data Scientist  | Remote			           	  	                         	  		                    Feb 2026 – present</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PROFESSIONAL SUMMARY
+Innovative data scientist with over 2 years of experience applying SQL, Python, and statistical analysis to drive data-informed product and operational decisions. Skilled in designing and analyzing experiments (including A/B testing), defining and monitoring core product metrics, and transforming ambiguous business questions into structured analytical insights. Proven experience building scalable data pipelines, behavioral models, and dashboards to analyze user engagement and customer experience across large datasets. Adept at collaborating with product managers, engineers, and cross-functional stakeholders to evaluate product changes, measure impact, and deliver actionable recommendations that improve user experience and operational efficiency.
+TECHNICAL SKILLS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Accenture , Data Scientist | India  				   		        			             June 2021 – June 2022
+Defined and maintained core business and product metrics using SQL and Tableau dashboards, enabling stakeholders to monitor system performance, user engagement trends, and operational KPIs.
+Conducted deep-dive analyses using SQL and Python to investigate performance issues and uncover behavioral patterns in large datasets, translating ambiguous business questions into structured analytical problems.
+Built scalable data pipelines using Google BigQuery, Dataflow, and GCS to process 1M+ records daily, ensuring reliable datasets for reporting, experimentation, and analytics workflows.
+EDUCATION</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Not mentioned in the resume</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>experience with python programming language and software development for varying lengths of time.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TECHNICAL SKILLS
+Big Data Technologies: Databricks, PySpark, Apache Spark
+Programming Languages: Python, SQL, PySpark, Excel VBA
+Databases: Snowflake, BigQuery, UnityCatalog, Azure SQL
+Machine Learning &amp; NLP: GPT-4o, prompt engineering, few-shot learning, sentiment analysis, RFM modeling, predictive modeling, anomaly detection, tokenization, lemmatization, text preprocessing
+Data Engineering &amp; Workflow Automation: ETL/ELT pipeline development, Databricks Jobs, MLflow, automated scoring pipelines
+Data Visualization: Tableau, Excel
+PROFESSIONAL EXPERIENCE
+BCBSND,  Data Scientist  | Remote			           	  	                         	  		                    Feb 2026 – present</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PROFESSIONAL SUMMARY
+Innovative data scientist with over 2 years of experience applying SQL, Python, and statistical analysis to drive data-informed product and operational decisions. Skilled in designing and analyzing experiments (including A/B testing), defining and monitoring core product metrics, and transforming ambiguous business questions into structured analytical insights. Proven experience building scalable data pipelines, behavioral models, and dashboards to analyze user engagement and customer experience across large datasets. Adept at collaborating with product managers, engineers, and cross-functional stakeholders to evaluate product changes, measure impact, and deliver actionable recommendations that improve user experience and operational efficiency.
+TECHNICAL SKILLS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PROFESSIONAL EXPERIENCE
+BCBSND,  Data Scientist  | Remote			           	  	                         	  		                    Feb 2026 – present
+Designed and deployed automated contract review workflows using Microsoft Copilot Studio, Microsoft Power Automate, and Azure Functions (Python) to analyze healthcare agreements and generate structured, standardized output documents, improving consistency and reducing manual review effort.
+Built a Compliance 360 Q&amp;A solution using Microsoft Copilot Studio integrated with a knowledge base of 400+ regulatory and internal policy documents, enabling efficient, real-time retrieval of compliance information.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>More than 2 years, as mentioned in the professional experience section under "BCBSND" where it states over 2 years of experience applying SQL, Python, and statistical analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>number of years experince in pthon</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TECHNICAL SKILLS
+Big Data Technologies: Databricks, PySpark, Apache Spark
+Programming Languages: Python, SQL, PySpark, Excel VBA
+Databases: Snowflake, BigQuery, UnityCatalog, Azure SQL
+Machine Learning &amp; NLP: GPT-4o, prompt engineering, few-shot learning, sentiment analysis, RFM modeling, predictive modeling, anomaly detection, tokenization, lemmatization, text preprocessing
+Data Engineering &amp; Workflow Automation: ETL/ELT pipeline development, Databricks Jobs, MLflow, automated scoring pipelines
+Data Visualization: Tableau, Excel
+PROFESSIONAL EXPERIENCE
+BCBSND,  Data Scientist  | Remote			           	  	                         	  		                    Feb 2026 – present</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PROFESSIONAL SUMMARY
+Innovative data scientist with over 2 years of experience applying SQL, Python, and statistical analysis to drive data-informed product and operational decisions. Skilled in designing and analyzing experiments (including A/B testing), defining and monitoring core product metrics, and transforming ambiguous business questions into structured analytical insights. Proven experience building scalable data pipelines, behavioral models, and dashboards to analyze user engagement and customer experience across large datasets. Adept at collaborating with product managers, engineers, and cross-functional stakeholders to evaluate product changes, measure impact, and deliver actionable recommendations that improve user experience and operational efficiency.
+TECHNICAL SKILLS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Accenture , Data Scientist | India  				   		        			             June 2021 – June 2022
+Defined and maintained core business and product metrics using SQL and Tableau dashboards, enabling stakeholders to monitor system performance, user engagement trends, and operational KPIs.
+Conducted deep-dive analyses using SQL and Python to investigate performance issues and uncover behavioral patterns in large datasets, translating ambiguous business questions into structured analytical problems.
+Built scalable data pipelines using Google BigQuery, Dataflow, and GCS to process 1M+ records daily, ensuring reliable datasets for reporting, experimentation, and analytics workflows.
+EDUCATION</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Over 2 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>number of years experince in pthon</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TECHNICAL SKILLS
+Big Data Technologies: Databricks, PySpark, Apache Spark
+Programming Languages: Python, SQL, PySpark, Excel VBA
+Databases: Snowflake, BigQuery, UnityCatalog, Azure SQL
+Machine Learning &amp; NLP: GPT-4o, prompt engineering, few-shot learning, sentiment analysis, RFM modeling, predictive modeling, anomaly detection, tokenization, lemmatization, text preprocessing
+Data Engineering &amp; Workflow Automation: ETL/ELT pipeline development, Databricks Jobs, MLflow, automated scoring pipelines
+Data Visualization: Tableau, Excel
+PROFESSIONAL EXPERIENCE
+BCBSND,  Data Scientist  | Remote			           	  	                         	  		                    Feb 2026 – present</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PROFESSIONAL SUMMARY
+Innovative data scientist with over 2 years of experience applying SQL, Python, and statistical analysis to drive data-informed product and operational decisions. Skilled in designing and analyzing experiments (including A/B testing), defining and monitoring core product metrics, and transforming ambiguous business questions into structured analytical insights. Proven experience building scalable data pipelines, behavioral models, and dashboards to analyze user engagement and customer experience across large datasets. Adept at collaborating with product managers, engineers, and cross-functional stakeholders to evaluate product changes, measure impact, and deliver actionable recommendations that improve user experience and operational efficiency.
+TECHNICAL SKILLS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Accenture , Data Scientist | India  				   		        			             June 2021 – June 2022
+Defined and maintained core business and product metrics using SQL and Tableau dashboards, enabling stakeholders to monitor system performance, user engagement trends, and operational KPIs.
+Conducted deep-dive analyses using SQL and Python to investigate performance issues and uncover behavioral patterns in large datasets, translating ambiguous business questions into structured analytical problems.
+Built scalable data pipelines using Google BigQuery, Dataflow, and GCS to process 1M+ records daily, ensuring reliable datasets for reporting, experimentation, and analytics workflows.
+EDUCATION</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Not mentioned in the resume</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>latest experience</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TECHNICAL SKILLS
+Big Data Technologies: Databricks, PySpark, Apache Spark
+Programming Languages: Python, SQL, PySpark, Excel VBA
+Databases: Snowflake, BigQuery, UnityCatalog, Azure SQL
+Machine Learning &amp; NLP: GPT-4o, prompt engineering, few-shot learning, sentiment analysis, RFM modeling, predictive modeling, anomaly detection, tokenization, lemmatization, text preprocessing
+Data Engineering &amp; Workflow Automation: ETL/ELT pipeline development, Databricks Jobs, MLflow, automated scoring pipelines
+Data Visualization: Tableau, Excel
+PROFESSIONAL EXPERIENCE
+BCBSND,  Data Scientist  | Remote			           	  	                         	  		                    Feb 2026 – present</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PROFESSIONAL SUMMARY
+Innovative data scientist with over 2 years of experience applying SQL, Python, and statistical analysis to drive data-informed product and operational decisions. Skilled in designing and analyzing experiments (including A/B testing), defining and monitoring core product metrics, and transforming ambiguous business questions into structured analytical insights. Proven experience building scalable data pipelines, behavioral models, and dashboards to analyze user engagement and customer experience across large datasets. Adept at collaborating with product managers, engineers, and cross-functional stakeholders to evaluate product changes, measure impact, and deliver actionable recommendations that improve user experience and operational efficiency.
+TECHNICAL SKILLS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Accenture , Data Scientist | India  				   		        			             June 2021 – June 2022
+Defined and maintained core business and product metrics using SQL and Tableau dashboards, enabling stakeholders to monitor system performance, user engagement trends, and operational KPIs.
+Conducted deep-dive analyses using SQL and Python to investigate performance issues and uncover behavioral patterns in large datasets, translating ambiguous business questions into structured analytical problems.
+Built scalable data pipelines using Google BigQuery, Dataflow, and GCS to process 1M+ records daily, ensuring reliable datasets for reporting, experimentation, and analytics workflows.
+EDUCATION</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>BCBSND, Data Scientist | Remote, Feb 2026 – present</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>latest work experience</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PROFESSIONAL EXPERIENCE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TECHNICAL SKILLS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EDUCATION</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Not mentioned in the resume</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>what is his latest work experince</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TECHNICAL SKILLS</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PROFESSIONAL EXPERIENCE</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Data Engineering &amp; Workflow Automation: ETL/ELT pipeline development, Databricks Jobs, MLflow, automated scoring pipelines</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Engineering &amp; Workflow Automation: ETL/ELT pipeline development, Databricks Jobs, MLflow, automated scoring pipelines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>experince related to pyython</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Programming Languages: Python, SQL, PySpark, Excel VBA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Innovative data scientist with over 2 years of experience applying SQL, Python, and statistical analysis to drive data-informed product and operational decisions. Skilled in designing and analyzing experiments (including A/B testing), defining and</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TECHNICAL SKILLS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Automated contract review workflows using Microsoft Copilot Studio, Microsoft Power Automate, and Azure Functions (Python) to analyze healthcare agreements and generate structured, standardized output documents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>machine learning and azure related experince?</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Masters in Computer Science</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Innovative data scientist with over 2 years of experience applying SQL, Python, and statistical analysis to drive data-informed product and operational decisions. Skilled in designing and analyzing experiments (including A/B testing), defining and</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Developed an EDI 834 data transformation pipeline leveraging Microsoft Power Automate and Azure Functions(Python) to process enrollment data and convert it into structured Excel reports, improving data accessibility and reducing manual processing time.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Not mentioned in the resume</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>azure related experince?</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Databases: Snowflake, BigQuery, UnityCatalog, Azure SQL</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Machine Learning &amp; NLP: GPT-4o, prompt engineering, few-shot learning, sentiment analysis, RFM modeling, predictive modeling, anomaly detection, tokenization, lemmatization, text preprocessing</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TECHNICAL SKILLS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Experience with Azure SQL database management and UnityCatalog data catalog management.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Binghamton, NY | (607) 595-8133 | chaitanya3168@gmail.com | https://www.linkedin.com/in/chaitanya-reddy-genai/</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Chaitanya Reddy</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VIT-AP University, India</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>most recent work experience</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Data Engineering &amp; Workflow Automation: ETL/ELT pipeline development, Databricks Jobs, MLflow, automated scoring pipelines</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>TECHNICAL SKILLS Big Data Technologies: Databricks, PySpark, Apache Spark Programming Languages: Python, SQL, PySpark, Excel VBA Databases: Snowflake, BigQuery, UnityCatalog, Azure SQL</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Built a Compliance 360 Q&amp;A solution using Microsoft Copilot Studio integrated with a knowledge base of 400+ regulatory and internal policy documents, enabling efficient, real-time retrieval of compliance information.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Built a Compliance 360 Q&amp;A solution using Microsoft Copilot Studio integrated with a knowledge base of 400+ regulatory and internal policy documents, enabling efficient, real-time retrieval of compliance information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>total ear working with pthon?</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Innovative data scientist with over 2 years of experience applying SQL, Python, and statistical analysis to drive data-informed product and operational decisions. Skilled in designing and analyzing experiments (including A/B testing), defining and</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>TECHNICAL SKILLS Big Data Technologies: Databricks, PySpark, Apache Spark Programming Languages: Python, SQL, PySpark, Excel VBA Databases: Snowflake, BigQuery, UnityCatalog, Azure SQL</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Masters in Computer Science VIT-AP University, India Bachelor of Science in Computer Science</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Over 2 years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>what are the skills?</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Innovative data scientist with over 2 years of experience applying SQL, Python, and statistical analysis to drive data-informed product and operational decisions. Skilled in designing and analyzing experiments (including A/B testing), defining and</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Data Visualization: Tableau, Excel PROFESSIONAL EXPERIENCE</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TECHNICAL SKILLS Big Data Technologies: Databricks, PySpark, Apache Spark Programming Languages: Python, SQL, PySpark, Excel VBA Databases: Snowflake, BigQuery, UnityCatalog, Azure SQL</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Python, SQL, PySpark, Excel VBA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>any known cloud technologies?</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Data Engineering &amp; Workflow Automation: ETL/ELT pipeline development, Databricks Jobs, MLflow, automated scoring pipelines</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>TECHNICAL SKILLS Big Data Technologies: Databricks, PySpark, Apache Spark Programming Languages: Python, SQL, PySpark, Excel VBA Databases: Snowflake, BigQuery, UnityCatalog, Azure SQL</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Developed an EDI 834 data transformation pipeline leveraging Microsoft Power Automate and Azure Functions(Python) to process enrollment data and convert it into structured Excel reports, improving data accessibility and reducing manual processing</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Azure Functions and Azure SQL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>what is his experince at UHG</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Developed an EDI 834 data transformation pipeline leveraging Microsoft Power Automate and Azure Functions(Python) to process enrollment data and convert it into structured Excel reports, improving data accessibility and reducing manual processing</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Implemented data validation, transformation, and error-handling logic using Python and Power Platform workflows, ensuring accuracy, consistency, and reliability of healthcare data pipelines.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Built scalable data pipelines using Google BigQuery, Dataflow, and GCS to process 1M+ records daily, ensuring reliable datasets for reporting, experimentation, and analytics workflows.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Not mentioned in the resume</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>what is his work experience at United Health Group</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>United Health Group,  Data Scientist  | Remote			           	  	                         	  		  Jan 2025 – Feb 2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PROFESSIONAL SUMMARY</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Designed and deployed automated contract review workflows using Microsoft Copilot Studio, Microsoft Power Automate, and Azure Functions (Python) to analyze healthcare agreements and generate structured, standardized output documents, improving</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Designed and deployed automated contract review workflows using Microsoft Copilot Studio, Microsoft Power Automate, and Azure Functions (Python) to analyze healthcare agreements.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
